--- a/demo/soc/fw/gen/wishbone/bus_regfiles.xlsx
+++ b/demo/soc/fw/gen/wishbone/bus_regfiles.xlsx
@@ -4,9 +4,9 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="sha256" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="smoke" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="soc_wb" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="regfile_sha256" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="regfile_smoke" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="bus_map_soc_wb" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -1267,10 +1267,10 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="10" max="12" width="16" customWidth="1"/>
+    <col min="9" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2197,10 +2197,10 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="10" max="12" width="16" customWidth="1"/>
+    <col min="9" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
